--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unit 7</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -460,72 +460,72 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.03267</v>
+        <v>17.54224</v>
       </c>
       <c r="D2" t="n">
-        <v>17.07176</v>
+        <v>16.84545</v>
       </c>
       <c r="E2" t="n">
-        <v>17.31098</v>
+        <v>17.45877</v>
       </c>
       <c r="F2" t="n">
-        <v>43.80111</v>
+        <v>44.28315</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05207</v>
+        <v>0.0524</v>
       </c>
       <c r="H2" t="n">
-        <v>1.90283</v>
+        <v>1.86604</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.0914</v>
+        <v>17.1581</v>
       </c>
       <c r="D3" t="n">
-        <v>16.99121</v>
+        <v>16.93401</v>
       </c>
       <c r="E3" t="n">
-        <v>16.94704</v>
+        <v>17.10409</v>
       </c>
       <c r="F3" t="n">
-        <v>44.46943</v>
+        <v>44.29042</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05278</v>
+        <v>0.05289</v>
       </c>
       <c r="H3" t="n">
-        <v>1.87403</v>
+        <v>1.89516</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.1985</v>
+        <v>17.36508</v>
       </c>
       <c r="D4" t="n">
-        <v>17.16988</v>
+        <v>17.09021</v>
       </c>
       <c r="E4" t="n">
-        <v>16.73676</v>
+        <v>17.36501</v>
       </c>
       <c r="F4" t="n">
-        <v>43.37473</v>
+        <v>43.09904</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05274</v>
+        <v>0.05359</v>
       </c>
       <c r="H4" t="n">
-        <v>1.88303</v>
+        <v>1.88133</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.44405</v>
+        <v>17.08733</v>
       </c>
       <c r="D5" t="n">
-        <v>17.38005</v>
+        <v>17.04863</v>
       </c>
       <c r="E5" t="n">
-        <v>17.10186</v>
+        <v>17.06577</v>
       </c>
       <c r="F5" t="n">
-        <v>43.77087</v>
+        <v>43.30519</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05208</v>
+        <v>0.05221</v>
       </c>
       <c r="H5" t="n">
-        <v>1.89211</v>
+        <v>1.88923</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.96241</v>
+        <v>17.58272</v>
       </c>
       <c r="D6" t="n">
-        <v>17.63504</v>
+        <v>17.23435</v>
       </c>
       <c r="E6" t="n">
-        <v>17.00838</v>
+        <v>17.27752</v>
       </c>
       <c r="F6" t="n">
-        <v>43.47573</v>
+        <v>43.94609</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05138</v>
+        <v>0.05215</v>
       </c>
       <c r="H6" t="n">
-        <v>1.87197</v>
+        <v>1.85729</v>
       </c>
     </row>
     <row r="7">
@@ -585,192 +585,1596 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.04648</v>
+        <v>17.33878</v>
       </c>
       <c r="D7" t="n">
-        <v>17.26945</v>
+        <v>16.82969</v>
       </c>
       <c r="E7" t="n">
-        <v>17.1469</v>
+        <v>16.84563</v>
       </c>
       <c r="F7" t="n">
-        <v>42.92757</v>
+        <v>43.60469</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05209</v>
+        <v>0.05211</v>
       </c>
       <c r="H7" t="n">
-        <v>1.91149</v>
+        <v>1.84711</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.28995</v>
+        <v>17.5176</v>
       </c>
       <c r="D8" t="n">
-        <v>17.2354</v>
+        <v>17.1364</v>
       </c>
       <c r="E8" t="n">
-        <v>17.30886</v>
+        <v>17.41733</v>
       </c>
       <c r="F8" t="n">
-        <v>43.79069</v>
+        <v>43.17269</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05272</v>
+        <v>0.0516</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9225</v>
+        <v>1.90701</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.43348</v>
+        <v>17.87523</v>
       </c>
       <c r="D9" t="n">
-        <v>17.27021</v>
+        <v>16.85857</v>
       </c>
       <c r="E9" t="n">
-        <v>16.97116</v>
+        <v>16.97767</v>
       </c>
       <c r="F9" t="n">
-        <v>43.74916</v>
+        <v>44.30316</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05201</v>
+        <v>0.05281</v>
       </c>
       <c r="H9" t="n">
-        <v>1.91508</v>
+        <v>1.86756</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.58157</v>
+        <v>17.28618</v>
       </c>
       <c r="D10" t="n">
-        <v>17.07534</v>
+        <v>17.22265</v>
       </c>
       <c r="E10" t="n">
-        <v>16.97101</v>
+        <v>17.28591</v>
       </c>
       <c r="F10" t="n">
-        <v>44.46915</v>
+        <v>42.77421</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05238</v>
+        <v>0.05249</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8407</v>
+        <v>1.90661</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>17.49869</v>
+      </c>
+      <c r="D11" t="n">
+        <v>17.2402</v>
+      </c>
+      <c r="E11" t="n">
+        <v>17.3165</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.7132</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05197</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.87329</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
-        </is>
+          <t>Unit 11</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>17.2384</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.97165</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.11133</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.31705</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05386</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.81567</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
-        </is>
+          <t>Unit 12</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>17.24064</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16.90558</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.06617</v>
+      </c>
+      <c r="F13" t="n">
+        <v>43.45256</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05201</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.88578</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
-        </is>
+          <t>Unit 13</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>17.4968</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16.61654</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17.12294</v>
+      </c>
+      <c r="F14" t="n">
+        <v>43.58881</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05167</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.84366</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
-        </is>
+          <t>Unit 14</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>17.36744</v>
+      </c>
+      <c r="D15" t="n">
+        <v>17.0902</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.35814</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43.16869</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05257</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.87034</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
-        </is>
+          <t>Unit 15</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>17.30342</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16.81322</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.99131</v>
+      </c>
+      <c r="F16" t="n">
+        <v>43.83085</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.84132</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
-        </is>
+          <t>Unit 16</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>17.352</v>
+      </c>
+      <c r="D17" t="n">
+        <v>17.08042</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.17947</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.6434</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05168</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.87347</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
-        </is>
+          <t>Unit 17</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>17.21056</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16.85952</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.16954</v>
+      </c>
+      <c r="F18" t="n">
+        <v>44.65237</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05253</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.87344</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
-        </is>
+          <t>Unit 18</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>17.67364</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.76105</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.31742</v>
+      </c>
+      <c r="F19" t="n">
+        <v>44.18286</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05179</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.84346</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Unit 19</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17.478</v>
+      </c>
+      <c r="D20" t="n">
+        <v>17.009</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17.27715</v>
+      </c>
+      <c r="F20" t="n">
+        <v>44.22028</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05173</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.88816</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>17.32332</v>
+      </c>
+      <c r="D21" t="n">
+        <v>17.13722</v>
+      </c>
+      <c r="E21" t="n">
+        <v>17.19275</v>
+      </c>
+      <c r="F21" t="n">
+        <v>42.35293</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.05225</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.87758</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 21</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>17.22885</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16.78403</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.88305</v>
+      </c>
+      <c r="F22" t="n">
+        <v>43.64869</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.87459</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 22</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>17.50986</v>
+      </c>
+      <c r="D23" t="n">
+        <v>17.08756</v>
+      </c>
+      <c r="E23" t="n">
+        <v>17.42271</v>
+      </c>
+      <c r="F23" t="n">
+        <v>44.12975</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.05276</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.8731</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 23</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>17.48405</v>
+      </c>
+      <c r="D24" t="n">
+        <v>17.05459</v>
+      </c>
+      <c r="E24" t="n">
+        <v>17.30566</v>
+      </c>
+      <c r="F24" t="n">
+        <v>43.75091</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.05132</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.89707</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 24</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>17.20899</v>
+      </c>
+      <c r="D25" t="n">
+        <v>17.01405</v>
+      </c>
+      <c r="E25" t="n">
+        <v>17.16273</v>
+      </c>
+      <c r="F25" t="n">
+        <v>43.19424</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.05336</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.89013</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 25</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>17.13286</v>
+      </c>
+      <c r="D26" t="n">
+        <v>16.87823</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.95201</v>
+      </c>
+      <c r="F26" t="n">
+        <v>44.14575</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.05179</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.85246</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 26</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>17.21256</v>
+      </c>
+      <c r="D27" t="n">
+        <v>16.72219</v>
+      </c>
+      <c r="E27" t="n">
+        <v>16.83126</v>
+      </c>
+      <c r="F27" t="n">
+        <v>44.13362</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.05131</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.90783</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 27</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>17.37871</v>
+      </c>
+      <c r="D28" t="n">
+        <v>16.96203</v>
+      </c>
+      <c r="E28" t="n">
+        <v>17.16094</v>
+      </c>
+      <c r="F28" t="n">
+        <v>44.83773</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.87684</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 28</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>17.11779</v>
+      </c>
+      <c r="D29" t="n">
+        <v>17.06493</v>
+      </c>
+      <c r="E29" t="n">
+        <v>17.10324</v>
+      </c>
+      <c r="F29" t="n">
+        <v>43.58521</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.05229</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.84641</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>17.43764</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16.95815</v>
+      </c>
+      <c r="E30" t="n">
+        <v>17.01954</v>
+      </c>
+      <c r="F30" t="n">
+        <v>44.91479</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.05217</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.90784</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>17.35812</v>
+      </c>
+      <c r="D31" t="n">
+        <v>17.24587</v>
+      </c>
+      <c r="E31" t="n">
+        <v>17.3538</v>
+      </c>
+      <c r="F31" t="n">
+        <v>44.43887</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.05139</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.87078</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>17.40912</v>
+      </c>
+      <c r="D32" t="n">
+        <v>17.11461</v>
+      </c>
+      <c r="E32" t="n">
+        <v>17.36386</v>
+      </c>
+      <c r="F32" t="n">
+        <v>43.80539</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.05175</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.88461</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17.52672</v>
+      </c>
+      <c r="D33" t="n">
+        <v>17.07904</v>
+      </c>
+      <c r="E33" t="n">
+        <v>17.09058</v>
+      </c>
+      <c r="F33" t="n">
+        <v>42.87059</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.05247</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.86256</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17.26656</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.99768</v>
+      </c>
+      <c r="E34" t="n">
+        <v>17.17135</v>
+      </c>
+      <c r="F34" t="n">
+        <v>43.90951</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.05171</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.85869</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>17.33624</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.78133</v>
+      </c>
+      <c r="E35" t="n">
+        <v>17.18934</v>
+      </c>
+      <c r="F35" t="n">
+        <v>44.12905</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0521</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.88762</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17.44968</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.67344</v>
+      </c>
+      <c r="E36" t="n">
+        <v>17.27549</v>
+      </c>
+      <c r="F36" t="n">
+        <v>42.82934</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.05192</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.86895</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.32648</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.62143</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.96177</v>
+      </c>
+      <c r="F37" t="n">
+        <v>43.50378</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.05113</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.87231</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>17.13597</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.37655</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.77687</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.54362</v>
+      </c>
+      <c r="G39" t="n">
+        <v>35.63897</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>17.11539</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.31788</v>
+      </c>
+      <c r="E40" t="n">
+        <v>17.10078</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22.37801</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.98483</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
+      </c>
+      <c r="C41" t="n">
+        <v>17.22545</v>
+      </c>
+      <c r="D41" t="n">
+        <v>16.42039</v>
+      </c>
+      <c r="E41" t="n">
+        <v>17.094</v>
+      </c>
+      <c r="F41" t="n">
+        <v>21.94222</v>
+      </c>
+      <c r="G41" t="n">
+        <v>34.6068</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>17.17412</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.40031</v>
+      </c>
+      <c r="E42" t="n">
+        <v>17.16679</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.14134</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.43392</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>17.12944</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.54814</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.84104</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.14911</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.95065</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>17.43547</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.35849</v>
+      </c>
+      <c r="E44" t="n">
+        <v>17.05907</v>
+      </c>
+      <c r="F44" t="n">
+        <v>23.03462</v>
+      </c>
+      <c r="G44" t="n">
+        <v>35.39136</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>17.43265</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.13049</v>
+      </c>
+      <c r="E45" t="n">
+        <v>17.08278</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22.48883</v>
+      </c>
+      <c r="G45" t="n">
+        <v>35.18095</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.8993</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.4804</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.66429</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.43984</v>
+      </c>
+      <c r="G46" t="n">
+        <v>35.46056</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>17.08976</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.13707</v>
+      </c>
+      <c r="E47" t="n">
+        <v>17.04139</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22.31919</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.83559</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>17.30442</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.77937</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.81477</v>
+      </c>
+      <c r="F48" t="n">
+        <v>23.13933</v>
+      </c>
+      <c r="G48" t="n">
+        <v>35.17945</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 11</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>17.40947</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.41305</v>
+      </c>
+      <c r="E49" t="n">
+        <v>17.31454</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22.84447</v>
+      </c>
+      <c r="G49" t="n">
+        <v>35.73</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 12</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>17.13249</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.47042</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.96241</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.13866</v>
+      </c>
+      <c r="G50" t="n">
+        <v>35.46782</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unit 13</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>17.11792</v>
+      </c>
+      <c r="D51" t="n">
+        <v>16.43243</v>
+      </c>
+      <c r="E51" t="n">
+        <v>16.82671</v>
+      </c>
+      <c r="F51" t="n">
+        <v>22.28487</v>
+      </c>
+      <c r="G51" t="n">
+        <v>35.51448</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 14</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>17.2186</v>
+      </c>
+      <c r="D52" t="n">
+        <v>16.61127</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.98492</v>
+      </c>
+      <c r="F52" t="n">
+        <v>22.63918</v>
+      </c>
+      <c r="G52" t="n">
+        <v>35.09552</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 15</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>17.51244</v>
+      </c>
+      <c r="D53" t="n">
+        <v>16.3342</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.71227</v>
+      </c>
+      <c r="F53" t="n">
+        <v>22.48402</v>
+      </c>
+      <c r="G53" t="n">
+        <v>35.06121</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 16</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>17.43096</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.80655</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.88566</v>
+      </c>
+      <c r="F54" t="n">
+        <v>22.48951</v>
+      </c>
+      <c r="G54" t="n">
+        <v>35.99765</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 17</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>17.34706</v>
+      </c>
+      <c r="D55" t="n">
+        <v>16.51183</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.95979</v>
+      </c>
+      <c r="F55" t="n">
+        <v>22.37053</v>
+      </c>
+      <c r="G55" t="n">
+        <v>35.50277</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 18</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>17.5352</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16.37122</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.46886</v>
+      </c>
+      <c r="F56" t="n">
+        <v>21.81518</v>
+      </c>
+      <c r="G56" t="n">
+        <v>34.66721</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 19</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>17.11609</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16.14214</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.71888</v>
+      </c>
+      <c r="F57" t="n">
+        <v>22.5502</v>
+      </c>
+      <c r="G57" t="n">
+        <v>35.333</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>17.29376</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16.67297</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.81416</v>
+      </c>
+      <c r="F58" t="n">
+        <v>22.1223</v>
+      </c>
+      <c r="G58" t="n">
+        <v>34.68558</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 21</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>17.08347</v>
+      </c>
+      <c r="D59" t="n">
+        <v>16.20494</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.71636</v>
+      </c>
+      <c r="F59" t="n">
+        <v>22.42669</v>
+      </c>
+      <c r="G59" t="n">
+        <v>34.81872</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 22</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>17.06336</v>
+      </c>
+      <c r="D60" t="n">
+        <v>16.45984</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.66227</v>
+      </c>
+      <c r="F60" t="n">
+        <v>22.31576</v>
+      </c>
+      <c r="G60" t="n">
+        <v>34.07168</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unit 23</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>17.41177</v>
+      </c>
+      <c r="D61" t="n">
+        <v>16.39252</v>
+      </c>
+      <c r="E61" t="n">
+        <v>16.60407</v>
+      </c>
+      <c r="F61" t="n">
+        <v>22.12781</v>
+      </c>
+      <c r="G61" t="n">
+        <v>35.12301</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 24</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>17.17178</v>
+      </c>
+      <c r="D62" t="n">
+        <v>16.58254</v>
+      </c>
+      <c r="E62" t="n">
+        <v>16.74771</v>
+      </c>
+      <c r="F62" t="n">
+        <v>22.29445</v>
+      </c>
+      <c r="G62" t="n">
+        <v>35.00056</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 25</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>17.23556</v>
+      </c>
+      <c r="D63" t="n">
+        <v>16.61497</v>
+      </c>
+      <c r="E63" t="n">
+        <v>16.93958</v>
+      </c>
+      <c r="F63" t="n">
+        <v>22.03438</v>
+      </c>
+      <c r="G63" t="n">
+        <v>35.64779</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 26</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>17.50087</v>
+      </c>
+      <c r="D64" t="n">
+        <v>16.2427</v>
+      </c>
+      <c r="E64" t="n">
+        <v>16.93403</v>
+      </c>
+      <c r="F64" t="n">
+        <v>22.69324</v>
+      </c>
+      <c r="G64" t="n">
+        <v>35.60304</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 27</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>17.41692</v>
+      </c>
+      <c r="D65" t="n">
+        <v>16.33092</v>
+      </c>
+      <c r="E65" t="n">
+        <v>16.87625</v>
+      </c>
+      <c r="F65" t="n">
+        <v>22.37529</v>
+      </c>
+      <c r="G65" t="n">
+        <v>35.40939</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 28</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>16.85233</v>
+      </c>
+      <c r="D66" t="n">
+        <v>16.51449</v>
+      </c>
+      <c r="E66" t="n">
+        <v>16.83201</v>
+      </c>
+      <c r="F66" t="n">
+        <v>22.15017</v>
+      </c>
+      <c r="G66" t="n">
+        <v>34.56102</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>17.17555</v>
+      </c>
+      <c r="D67" t="n">
+        <v>16.51673</v>
+      </c>
+      <c r="E67" t="n">
+        <v>16.97686</v>
+      </c>
+      <c r="F67" t="n">
+        <v>22.36955</v>
+      </c>
+      <c r="G67" t="n">
+        <v>35.57377</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>17.19788</v>
+      </c>
+      <c r="D68" t="n">
+        <v>16.31869</v>
+      </c>
+      <c r="E68" t="n">
+        <v>16.92268</v>
+      </c>
+      <c r="F68" t="n">
+        <v>22.30863</v>
+      </c>
+      <c r="G68" t="n">
+        <v>35.61116</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>17.13478</v>
+      </c>
+      <c r="D69" t="n">
+        <v>16.25051</v>
+      </c>
+      <c r="E69" t="n">
+        <v>16.93245</v>
+      </c>
+      <c r="F69" t="n">
+        <v>22.10721</v>
+      </c>
+      <c r="G69" t="n">
+        <v>35.09325</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>17.3248</v>
+      </c>
+      <c r="D70" t="n">
+        <v>16.14104</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16.67678</v>
+      </c>
+      <c r="F70" t="n">
+        <v>22.21454</v>
+      </c>
+      <c r="G70" t="n">
+        <v>35.2996</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>17.38974</v>
+      </c>
+      <c r="D71" t="n">
+        <v>16.57745</v>
+      </c>
+      <c r="E71" t="n">
+        <v>16.90029</v>
+      </c>
+      <c r="F71" t="n">
+        <v>22.27207</v>
+      </c>
+      <c r="G71" t="n">
+        <v>34.90126</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>16.94394</v>
+      </c>
+      <c r="D72" t="n">
+        <v>16.46051</v>
+      </c>
+      <c r="E72" t="n">
+        <v>16.8132</v>
+      </c>
+      <c r="F72" t="n">
+        <v>22.33774</v>
+      </c>
+      <c r="G72" t="n">
+        <v>35.42268</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>17.39022</v>
+      </c>
+      <c r="D73" t="n">
+        <v>16.50095</v>
+      </c>
+      <c r="E73" t="n">
+        <v>16.72351</v>
+      </c>
+      <c r="F73" t="n">
+        <v>22.00814</v>
+      </c>
+      <c r="G73" t="n">
+        <v>35.61722</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>17.24086</v>
+      </c>
+      <c r="D74" t="n">
+        <v>16.59012</v>
+      </c>
+      <c r="E74" t="n">
+        <v>16.84448</v>
+      </c>
+      <c r="F74" t="n">
+        <v>22.38936</v>
+      </c>
+      <c r="G74" t="n">
+        <v>35.05766</v>
       </c>
     </row>
   </sheetData>
